--- a/relatorio-fai-faculdade-de-ensino-superior-todos-os-semestres-2026-08-11.xlsx
+++ b/relatorio-fai-faculdade-de-ensino-superior-todos-os-semestres-2026-08-11.xlsx
@@ -33,8 +33,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -65,8 +66,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,7 +448,7 @@
         <v>Gerado em</v>
       </c>
       <c r="B6" t="str">
-        <v>11/08/2026, 23:17:42</v>
+        <v>11/08/2026, 23:19:01</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +545,7 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>41</v>
       </c>
     </row>
@@ -560,7 +562,7 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>42</v>
       </c>
     </row>
@@ -577,7 +579,7 @@
       <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>43</v>
       </c>
     </row>
@@ -591,7 +593,7 @@
       <c r="E9">
         <v>2</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>44</v>
       </c>
     </row>
@@ -608,7 +610,7 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>45</v>
       </c>
     </row>
@@ -625,7 +627,7 @@
       <c r="E11">
         <v>2</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>46</v>
       </c>
     </row>
@@ -642,7 +644,7 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>37</v>
       </c>
     </row>
@@ -656,7 +658,7 @@
       <c r="E13">
         <v>2</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>48</v>
       </c>
     </row>
@@ -673,7 +675,7 @@
       <c r="E14">
         <v>2</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>49</v>
       </c>
     </row>
@@ -690,7 +692,7 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>50</v>
       </c>
     </row>
@@ -707,7 +709,7 @@
       <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>51</v>
       </c>
     </row>
@@ -721,7 +723,7 @@
       <c r="E17">
         <v>2</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>52</v>
       </c>
     </row>
@@ -738,7 +740,7 @@
       <c r="E18">
         <v>2</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>53</v>
       </c>
     </row>
@@ -755,7 +757,7 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>44</v>
       </c>
     </row>
@@ -772,7 +774,7 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>55</v>
       </c>
     </row>
@@ -786,7 +788,7 @@
       <c r="E21">
         <v>2</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>56</v>
       </c>
     </row>
@@ -803,7 +805,7 @@
       <c r="E22">
         <v>2</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>57</v>
       </c>
     </row>
@@ -820,7 +822,7 @@
       <c r="E23">
         <v>2</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>58</v>
       </c>
     </row>
@@ -837,7 +839,7 @@
       <c r="E24">
         <v>2</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>59</v>
       </c>
     </row>
@@ -851,7 +853,7 @@
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>60</v>
       </c>
     </row>
@@ -868,7 +870,7 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>51</v>
       </c>
     </row>
@@ -885,7 +887,7 @@
       <c r="E27">
         <v>2</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>62</v>
       </c>
     </row>
@@ -902,7 +904,7 @@
       <c r="E28">
         <v>2</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>63</v>
       </c>
     </row>
@@ -916,7 +918,7 @@
       <c r="E29">
         <v>2</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>64</v>
       </c>
     </row>
@@ -933,7 +935,7 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>65</v>
       </c>
     </row>
@@ -950,7 +952,7 @@
       <c r="E31">
         <v>2</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>66</v>
       </c>
     </row>
@@ -967,7 +969,7 @@
       <c r="E32">
         <v>2</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>67</v>
       </c>
     </row>
@@ -981,7 +983,7 @@
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>58</v>
       </c>
     </row>
@@ -998,7 +1000,7 @@
       <c r="E34">
         <v>2</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1">
         <v>69</v>
       </c>
     </row>
@@ -1015,7 +1017,7 @@
       <c r="E35">
         <v>1</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1">
         <v>70</v>
       </c>
     </row>
@@ -1032,7 +1034,7 @@
       <c r="E36">
         <v>2</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="1">
         <v>71</v>
       </c>
     </row>
@@ -1046,7 +1048,7 @@
       <c r="E37">
         <v>2</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1">
         <v>72</v>
       </c>
     </row>
@@ -1063,7 +1065,7 @@
       <c r="E38">
         <v>2</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="1">
         <v>73</v>
       </c>
     </row>
@@ -1080,7 +1082,7 @@
       <c r="E39">
         <v>2</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>74</v>
       </c>
     </row>
@@ -1108,7 +1110,7 @@
       <c r="E41">
         <v>2</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="1">
         <v>76</v>
       </c>
     </row>
@@ -1125,7 +1127,7 @@
       <c r="E42">
         <v>2</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="1">
         <v>77</v>
       </c>
     </row>
@@ -1142,7 +1144,7 @@
       <c r="E43">
         <v>2</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="1">
         <v>78</v>
       </c>
     </row>
@@ -1159,7 +1161,7 @@
       <c r="E44">
         <v>2</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="1">
         <v>79</v>
       </c>
     </row>
@@ -1173,7 +1175,7 @@
       <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="1">
         <v>80</v>
       </c>
     </row>
@@ -1190,7 +1192,7 @@
       <c r="E46">
         <v>2</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="1">
         <v>81</v>
       </c>
     </row>
@@ -1207,7 +1209,7 @@
       <c r="E47">
         <v>1</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="1">
         <v>72</v>
       </c>
     </row>
@@ -1224,7 +1226,7 @@
       <c r="E48">
         <v>2</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="1">
         <v>83</v>
       </c>
     </row>
@@ -1238,7 +1240,7 @@
       <c r="E49">
         <v>2</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="1">
         <v>84</v>
       </c>
     </row>
@@ -1255,7 +1257,7 @@
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="1">
         <v>85</v>
       </c>
     </row>
@@ -1272,7 +1274,7 @@
       <c r="E51">
         <v>2</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="1">
         <v>86</v>
       </c>
     </row>
@@ -1289,7 +1291,7 @@
       <c r="E52">
         <v>2</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="1">
         <v>87</v>
       </c>
     </row>
@@ -1303,7 +1305,7 @@
       <c r="E53">
         <v>2</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="1">
         <v>88</v>
       </c>
     </row>
@@ -1320,7 +1322,7 @@
       <c r="E54">
         <v>1</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="1">
         <v>79</v>
       </c>
     </row>
@@ -1337,7 +1339,7 @@
       <c r="E55">
         <v>1</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="1">
         <v>40</v>
       </c>
     </row>
@@ -1354,7 +1356,7 @@
       <c r="E56">
         <v>2</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="1">
         <v>41</v>
       </c>
     </row>
@@ -1368,7 +1370,7 @@
       <c r="E57">
         <v>2</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="1">
         <v>42</v>
       </c>
     </row>
@@ -1385,7 +1387,7 @@
       <c r="E58">
         <v>2</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="1">
         <v>43</v>
       </c>
     </row>
@@ -1402,7 +1404,7 @@
       <c r="E59">
         <v>2</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="1">
         <v>44</v>
       </c>
     </row>
@@ -1419,7 +1421,7 @@
       <c r="E60">
         <v>1</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="1">
         <v>45</v>
       </c>
     </row>
@@ -1433,7 +1435,7 @@
       <c r="E61">
         <v>1</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="1">
         <v>86</v>
       </c>
     </row>
@@ -1450,7 +1452,7 @@
       <c r="E62">
         <v>2</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="1">
         <v>47</v>
       </c>
     </row>
@@ -1467,7 +1469,7 @@
       <c r="E63">
         <v>2</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="1">
         <v>48</v>
       </c>
     </row>
@@ -1484,7 +1486,7 @@
       <c r="E64">
         <v>2</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="1">
         <v>49</v>
       </c>
     </row>
@@ -1498,7 +1500,7 @@
       <c r="E65">
         <v>1</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="1">
         <v>50</v>
       </c>
     </row>
@@ -1515,7 +1517,7 @@
       <c r="E66">
         <v>2</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="1">
         <v>51</v>
       </c>
     </row>
@@ -1532,7 +1534,7 @@
       <c r="E67">
         <v>2</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="1">
         <v>52</v>
       </c>
     </row>
@@ -1549,7 +1551,7 @@
       <c r="E68">
         <v>1</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="1">
         <v>33</v>
       </c>
     </row>
@@ -1563,7 +1565,7 @@
       <c r="E69">
         <v>2</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="1">
         <v>54</v>
       </c>
     </row>
@@ -1580,7 +1582,7 @@
       <c r="E70">
         <v>1</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="1">
         <v>55</v>
       </c>
     </row>
@@ -1597,7 +1599,7 @@
       <c r="E71">
         <v>2</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="1">
         <v>56</v>
       </c>
     </row>
@@ -1614,7 +1616,7 @@
       <c r="E72">
         <v>2</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="1">
         <v>57</v>
       </c>
     </row>
@@ -1628,7 +1630,7 @@
       <c r="E73">
         <v>2</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="1">
         <v>58</v>
       </c>
     </row>
@@ -1645,7 +1647,7 @@
       <c r="E74">
         <v>2</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="1">
         <v>59</v>
       </c>
     </row>
@@ -1676,7 +1678,7 @@
       <c r="E76">
         <v>2</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="1">
         <v>61</v>
       </c>
     </row>
@@ -1690,7 +1692,7 @@
       <c r="E77">
         <v>2</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="1">
         <v>62</v>
       </c>
     </row>
@@ -1707,7 +1709,7 @@
       <c r="E78">
         <v>2</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="1">
         <v>63</v>
       </c>
     </row>
@@ -1724,7 +1726,7 @@
       <c r="E79">
         <v>2</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="1">
         <v>64</v>
       </c>
     </row>
@@ -1741,7 +1743,7 @@
       <c r="E80">
         <v>1</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="1">
         <v>65</v>
       </c>
     </row>
@@ -1755,7 +1757,7 @@
       <c r="E81">
         <v>2</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="1">
         <v>66</v>
       </c>
     </row>
@@ -1772,7 +1774,7 @@
       <c r="E82">
         <v>1</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="1">
         <v>47</v>
       </c>
     </row>
@@ -1789,7 +1791,7 @@
       <c r="E83">
         <v>2</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="1">
         <v>68</v>
       </c>
     </row>
@@ -1806,7 +1808,7 @@
       <c r="E84">
         <v>2</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="1">
         <v>69</v>
       </c>
     </row>
@@ -1820,7 +1822,7 @@
       <c r="E85">
         <v>1</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="1">
         <v>70</v>
       </c>
     </row>
@@ -1837,7 +1839,7 @@
       <c r="E86">
         <v>2</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="1">
         <v>71</v>
       </c>
     </row>
@@ -1854,7 +1856,7 @@
       <c r="E87">
         <v>2</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="1">
         <v>72</v>
       </c>
     </row>
@@ -1871,7 +1873,7 @@
       <c r="E88">
         <v>2</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="1">
         <v>73</v>
       </c>
     </row>
@@ -1885,7 +1887,7 @@
       <c r="E89">
         <v>1</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="1">
         <v>54</v>
       </c>
     </row>
@@ -1902,7 +1904,7 @@
       <c r="E90">
         <v>1</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="1">
         <v>75</v>
       </c>
     </row>
@@ -1919,7 +1921,7 @@
       <c r="E91">
         <v>2</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="1">
         <v>76</v>
       </c>
     </row>
@@ -1936,7 +1938,7 @@
       <c r="E92">
         <v>2</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="1">
         <v>77</v>
       </c>
     </row>
@@ -1950,7 +1952,7 @@
       <c r="E93">
         <v>2</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="1">
         <v>78</v>
       </c>
     </row>
@@ -1967,7 +1969,7 @@
       <c r="E94">
         <v>2</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="1">
         <v>79</v>
       </c>
     </row>
@@ -1984,7 +1986,7 @@
       <c r="E95">
         <v>1</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="1">
         <v>80</v>
       </c>
     </row>
@@ -2001,7 +2003,7 @@
       <c r="E96">
         <v>1</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="1">
         <v>61</v>
       </c>
     </row>
@@ -2015,7 +2017,7 @@
       <c r="E97">
         <v>2</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="1">
         <v>82</v>
       </c>
     </row>
@@ -2032,7 +2034,7 @@
       <c r="E98">
         <v>2</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="1">
         <v>83</v>
       </c>
     </row>
@@ -2049,7 +2051,7 @@
       <c r="E99">
         <v>2</v>
       </c>
-      <c r="F99">
+      <c r="F99" s="1">
         <v>84</v>
       </c>
     </row>
@@ -2066,7 +2068,7 @@
       <c r="E100">
         <v>1</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="1">
         <v>85</v>
       </c>
     </row>
@@ -2080,7 +2082,7 @@
       <c r="E101">
         <v>2</v>
       </c>
-      <c r="F101">
+      <c r="F101" s="1">
         <v>86</v>
       </c>
     </row>
@@ -2097,7 +2099,7 @@
       <c r="E102">
         <v>2</v>
       </c>
-      <c r="F102">
+      <c r="F102" s="1">
         <v>87</v>
       </c>
     </row>
@@ -2114,7 +2116,7 @@
       <c r="E103">
         <v>1</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="1">
         <v>68</v>
       </c>
     </row>
@@ -2131,7 +2133,7 @@
       <c r="E104">
         <v>2</v>
       </c>
-      <c r="F104">
+      <c r="F104" s="1">
         <v>89</v>
       </c>
     </row>
@@ -2145,7 +2147,7 @@
       <c r="E105">
         <v>1</v>
       </c>
-      <c r="F105">
+      <c r="F105" s="1">
         <v>40</v>
       </c>
     </row>
@@ -2162,7 +2164,7 @@
       <c r="E106">
         <v>2</v>
       </c>
-      <c r="F106">
+      <c r="F106" s="1">
         <v>41</v>
       </c>
     </row>
@@ -2179,7 +2181,7 @@
       <c r="E107">
         <v>2</v>
       </c>
-      <c r="F107">
+      <c r="F107" s="1">
         <v>42</v>
       </c>
     </row>
@@ -2196,7 +2198,7 @@
       <c r="E108">
         <v>2</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="1">
         <v>43</v>
       </c>
     </row>
@@ -2210,7 +2212,7 @@
       <c r="E109">
         <v>2</v>
       </c>
-      <c r="F109">
+      <c r="F109" s="1">
         <v>44</v>
       </c>
     </row>
@@ -2241,7 +2243,7 @@
       <c r="E111">
         <v>2</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="1">
         <v>46</v>
       </c>
     </row>
@@ -2258,7 +2260,7 @@
       <c r="E112">
         <v>2</v>
       </c>
-      <c r="F112">
+      <c r="F112" s="1">
         <v>47</v>
       </c>
     </row>
@@ -2272,7 +2274,7 @@
       <c r="E113">
         <v>2</v>
       </c>
-      <c r="F113">
+      <c r="F113" s="1">
         <v>48</v>
       </c>
     </row>
@@ -2289,7 +2291,7 @@
       <c r="E114">
         <v>2</v>
       </c>
-      <c r="F114">
+      <c r="F114" s="1">
         <v>49</v>
       </c>
     </row>
@@ -2306,7 +2308,7 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115">
+      <c r="F115" s="1">
         <v>50</v>
       </c>
     </row>
@@ -2323,7 +2325,7 @@
       <c r="E116">
         <v>2</v>
       </c>
-      <c r="F116">
+      <c r="F116" s="1">
         <v>51</v>
       </c>
     </row>
@@ -2337,7 +2339,7 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117">
+      <c r="F117" s="1">
         <v>82</v>
       </c>
     </row>
@@ -2354,7 +2356,7 @@
       <c r="E118">
         <v>2</v>
       </c>
-      <c r="F118">
+      <c r="F118" s="1">
         <v>53</v>
       </c>
     </row>
@@ -2371,7 +2373,7 @@
       <c r="E119">
         <v>2</v>
       </c>
-      <c r="F119">
+      <c r="F119" s="1">
         <v>54</v>
       </c>
     </row>
@@ -2388,7 +2390,7 @@
       <c r="E120">
         <v>1</v>
       </c>
-      <c r="F120">
+      <c r="F120" s="1">
         <v>55</v>
       </c>
     </row>
@@ -2402,7 +2404,7 @@
       <c r="E121">
         <v>2</v>
       </c>
-      <c r="F121">
+      <c r="F121" s="1">
         <v>56</v>
       </c>
     </row>
@@ -2419,7 +2421,7 @@
       <c r="E122">
         <v>2</v>
       </c>
-      <c r="F122">
+      <c r="F122" s="1">
         <v>57</v>
       </c>
     </row>
@@ -2436,7 +2438,7 @@
       <c r="E123">
         <v>2</v>
       </c>
-      <c r="F123">
+      <c r="F123" s="1">
         <v>58</v>
       </c>
     </row>
@@ -2453,7 +2455,7 @@
       <c r="E124">
         <v>1</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="1">
         <v>89</v>
       </c>
     </row>
@@ -2467,7 +2469,7 @@
       <c r="E125">
         <v>1</v>
       </c>
-      <c r="F125">
+      <c r="F125" s="1">
         <v>60</v>
       </c>
     </row>
@@ -2484,7 +2486,7 @@
       <c r="E126">
         <v>2</v>
       </c>
-      <c r="F126">
+      <c r="F126" s="1">
         <v>61</v>
       </c>
     </row>
@@ -2501,7 +2503,7 @@
       <c r="E127">
         <v>2</v>
       </c>
-      <c r="F127">
+      <c r="F127" s="1">
         <v>62</v>
       </c>
     </row>
@@ -2518,7 +2520,7 @@
       <c r="E128">
         <v>2</v>
       </c>
-      <c r="F128">
+      <c r="F128" s="1">
         <v>63</v>
       </c>
     </row>
@@ -2532,7 +2534,7 @@
       <c r="E129">
         <v>2</v>
       </c>
-      <c r="F129">
+      <c r="F129" s="1">
         <v>64</v>
       </c>
     </row>
@@ -2549,7 +2551,7 @@
       <c r="E130">
         <v>1</v>
       </c>
-      <c r="F130">
+      <c r="F130" s="1">
         <v>65</v>
       </c>
     </row>
@@ -2566,7 +2568,7 @@
       <c r="E131">
         <v>1</v>
       </c>
-      <c r="F131">
+      <c r="F131" s="1">
         <v>36</v>
       </c>
     </row>
@@ -2583,7 +2585,7 @@
       <c r="E132">
         <v>2</v>
       </c>
-      <c r="F132">
+      <c r="F132" s="1">
         <v>67</v>
       </c>
     </row>
@@ -2597,7 +2599,7 @@
       <c r="E133">
         <v>2</v>
       </c>
-      <c r="F133">
+      <c r="F133" s="1">
         <v>68</v>
       </c>
     </row>
@@ -2614,7 +2616,7 @@
       <c r="E134">
         <v>2</v>
       </c>
-      <c r="F134">
+      <c r="F134" s="1">
         <v>69</v>
       </c>
     </row>
